--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7242" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7242" uniqueCount="747">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -518,7 +518,7 @@
     <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/structuredefinition-compliesWithProfile</t>
+    <t>http://hl7.org/fhir/StructureDefinition/structuredefinition-imposeProfile</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -1307,7 +1307,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|Organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|PractitionerRole|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
+    <t xml:space="preserve">Reference(http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner|http://hl7.dk/fhir/core/StructureDefinition/dk-core-organization|http://hl7.dk/fhir/core/StructureDefinition/dk-core-patient|http://hl7.dk/fhir/core/StructureDefinition/dk-core-practitioner-role|CareTeam|http://hl7.dk/fhir/core/StructureDefinition/dk-core-related-person)
 </t>
   </si>
   <si>
@@ -1715,6 +1715,9 @@
   </si>
   <si>
     <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct|http://snomed.info/sct/554471000005108</t>
   </si>
   <si>
     <t>Observation.method.coding:SCTCode.version</t>
@@ -14658,7 +14661,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>314</v>
+        <v>551</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14732,10 +14735,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14852,10 +14855,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14972,10 +14975,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15092,10 +15095,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15214,10 +15217,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15336,10 +15339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15362,16 +15365,16 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15421,7 +15424,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15439,27 +15442,27 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15482,16 +15485,16 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15541,7 +15544,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15559,27 +15562,27 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15602,19 +15605,19 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15663,7 +15666,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15675,7 +15678,7 @@
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15684,10 +15687,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15698,10 +15701,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15816,10 +15819,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15936,14 +15939,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15965,10 +15968,10 @@
         <v>139</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>142</v>
@@ -16023,7 +16026,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16058,10 +16061,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16084,13 +16087,13 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16141,7 +16144,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16150,7 +16153,7 @@
         <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -16162,10 +16165,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16176,10 +16179,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16202,13 +16205,13 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16259,7 +16262,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16268,7 +16271,7 @@
         <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>105</v>
@@ -16280,10 +16283,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16294,10 +16297,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16323,16 +16326,16 @@
         <v>220</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16360,10 +16363,10 @@
         <v>117</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16381,7 +16384,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16399,10 +16402,10 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>510</v>
@@ -16416,10 +16419,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16445,16 +16448,16 @@
         <v>220</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16482,10 +16485,10 @@
         <v>235</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16503,7 +16506,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16521,10 +16524,10 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>510</v>
@@ -16538,10 +16541,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16564,17 +16567,17 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16623,7 +16626,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16647,7 +16650,7 @@
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16658,10 +16661,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16687,10 +16690,10 @@
         <v>146</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16741,7 +16744,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16762,10 +16765,10 @@
         <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16776,10 +16779,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16802,16 +16805,16 @@
         <v>94</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16861,7 +16864,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16882,10 +16885,10 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -16896,10 +16899,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16922,16 +16925,16 @@
         <v>94</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16981,7 +16984,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17002,10 +17005,10 @@
         <v>82</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -17016,10 +17019,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17042,19 +17045,19 @@
         <v>94</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -17103,7 +17106,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17124,10 +17127,10 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -17138,10 +17141,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17256,10 +17259,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17376,14 +17379,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -17405,10 +17408,10 @@
         <v>139</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>142</v>
@@ -17463,7 +17466,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17498,10 +17501,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17527,13 +17530,13 @@
         <v>220</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>234</v>
@@ -17585,7 +17588,7 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>93</v>
@@ -17603,7 +17606,7 @@
         <v>82</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>240</v>
@@ -17620,10 +17623,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17738,10 +17741,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17858,10 +17861,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17978,10 +17981,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C128" t="s" s="2">
         <v>258</v>
@@ -18102,10 +18105,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18220,10 +18223,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18340,10 +18343,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18462,10 +18465,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18582,10 +18585,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18702,10 +18705,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18822,10 +18825,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18944,10 +18947,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>309</v>
@@ -19068,10 +19071,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19186,10 +19189,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19306,10 +19309,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19428,10 +19431,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19548,10 +19551,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19668,10 +19671,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19788,10 +19791,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19910,10 +19913,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>320</v>
@@ -20034,10 +20037,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20152,10 +20155,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20272,10 +20275,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20394,10 +20397,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20514,10 +20517,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20634,10 +20637,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20754,10 +20757,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20876,10 +20879,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>331</v>
@@ -21000,10 +21003,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21118,10 +21121,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21238,10 +21241,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21360,10 +21363,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21480,10 +21483,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21600,10 +21603,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21720,10 +21723,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21842,10 +21845,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>342</v>
@@ -21966,10 +21969,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22084,10 +22087,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22204,10 +22207,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22326,10 +22329,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22446,10 +22449,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22566,10 +22569,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22686,10 +22689,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22808,10 +22811,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>353</v>
@@ -22839,7 +22842,7 @@
         <v>248</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M168" t="s" s="2">
         <v>250</v>
@@ -22932,10 +22935,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23050,10 +23053,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23170,10 +23173,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23292,10 +23295,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23412,10 +23415,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23532,10 +23535,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23652,10 +23655,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23774,10 +23777,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23896,10 +23899,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23925,13 +23928,13 @@
         <v>427</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>429</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O177" t="s" s="2">
         <v>431</v>
@@ -23981,7 +23984,7 @@
         <v>156</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23999,7 +24002,7 @@
         <v>82</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>434</v>
@@ -24016,10 +24019,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>438</v>
@@ -24047,13 +24050,13 @@
         <v>439</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M178" t="s" s="2">
         <v>429</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>431</v>
@@ -24105,7 +24108,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24123,7 +24126,7 @@
         <v>82</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>434</v>
@@ -24140,10 +24143,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24258,10 +24261,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24378,10 +24381,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24500,10 +24503,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24622,10 +24625,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24742,10 +24745,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24862,10 +24865,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24984,10 +24987,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25013,13 +25016,13 @@
         <v>220</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="O186" t="s" s="2">
         <v>494</v>
@@ -25071,7 +25074,7 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25106,10 +25109,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25193,7 +25196,7 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25228,10 +25231,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25257,16 +25260,16 @@
         <v>83</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
@@ -25315,7 +25318,7 @@
         <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25336,10 +25339,10 @@
         <v>82</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1929,7 +1929,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-IPADkCoreObservation.xlsx
+++ b/StructureDefinition-IPADkCoreObservation.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Danish Core IPA Observation Profiles</t>
+    <t>Danish Core IPA Observation Profile</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
